--- a/output/laminas_comunales/comunal_s_fonasa_a_2024_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2024_tarapaca.xlsx
@@ -375,106 +375,106 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1101</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>Camiña</t>
         </is>
       </c>
       <c r="C2">
-        <v>165592</v>
+        <v>93.40823970037454</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
+          <t>Huara</t>
         </is>
       </c>
       <c r="C3">
-        <v>125416</v>
+        <v>92.62672811059907</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Alto Hospicio</t>
         </is>
       </c>
       <c r="C4">
-        <v>16488</v>
+        <v>89.75981220119664</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pica</t>
+          <t>Colchane</t>
         </is>
       </c>
       <c r="C5">
-        <v>6224</v>
+        <v>88.15697266993693</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1404</t>
+          <t>1405</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huara</t>
+          <t>Pica</t>
         </is>
       </c>
       <c r="C6">
-        <v>2814</v>
+        <v>87.71138669673056</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Colchane</t>
+          <t>Pozo Almonte</t>
         </is>
       </c>
       <c r="C7">
-        <v>1258</v>
+        <v>85.90632001250457</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1101</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Camiña</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="C8">
-        <v>1247</v>
+        <v>78.01853500873982</v>
       </c>
     </row>
   </sheetData>
@@ -530,7 +530,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2024_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2024_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C221"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -475,6 +475,3201 @@
       </c>
       <c r="C8">
         <v>78.01853500873982</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>50.10511562718991</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>48.31460674157304</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>48.18959842001317</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>45.55981792676992</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>45.51860202931229</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>45.0936329588015</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>45.05809409680613</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>44.43712969058591</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>44.19999427442673</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>42.19278466741827</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>40.84822591569843</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>40.39585954100647</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>39.8501872659176</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>38.05185704274702</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>37.62267546773335</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>36.07636603028308</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>33.70786516853933</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>33.14646110721794</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>31.23765635286373</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>31.00585638430696</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>31.00338218714769</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>29.99299229152067</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>28.96281240159171</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>28.37492835929766</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>26.77349632131917</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>24.48979591836735</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>23.54847801578354</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>23.2428489553483</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>23.07116104868914</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>21.54094050799305</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>21.4557390715365</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>21.10517878102545</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>21.08229988726043</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>20.76736995791704</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>19.40529875986471</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>18.57042747021724</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>18.19934351065493</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>17.44919411352488</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>16.53819201121233</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>16.47940074906367</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>16.45819618169849</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>15.85339669634422</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>14.25596175317054</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>13.96342416506018</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>13.90924464487035</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>13.85780118499012</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>13.5884134993663</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>13.58678537688586</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>13.48711642567386</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>13.47439539781481</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>13.40984796015963</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>13.3173618940248</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>13.25613352036873</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>13.17449194113525</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>13.0348913759052</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>12.95880149812734</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>12.90574688688584</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>12.8328036263221</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>12.67281105990783</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>12.62114423289846</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>12.58426966292135</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>12.54379817799579</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>12.40364400840925</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>12.26488824050435</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>12.0772266065389</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>11.8833246170735</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>11.66854565952649</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>11.42198815009875</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>11.16387981926717</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>11.08614232209738</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>11.02029312288613</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>10.36758180412814</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>10.33707865168539</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>10.17037461574532</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>10.02969832751524</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>9.887640449438202</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>9.643481415520597</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>9.611048478015784</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>9.588014981273409</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>9.497425169731493</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>8.854509545753785</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>8.779594137542277</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>8.591178406846609</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>8.558262014483212</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>8.479327259985984</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>8.372844266138696</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>8.326414932295096</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>8.195639985488604</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>8.058864751226348</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>7.731558043223226</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>7.265917602996255</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>6.341600901916573</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>6.264492857347342</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>5.956552207428171</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>5.742837354591584</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>5.288386390871672</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>4.324954911110475</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>4.117372683712844</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>3.903607666290868</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>3.595060699213255</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>3.255355129650507</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>3.025965474793164</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>2.887202174824615</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>2.74208822739544</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>2.466465957116001</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>2.437993235625705</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>2.312543798177996</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>2.288842716269252</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>2.164930481938496</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>2.069287198405631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>1.830414564163451</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>1.810401579986833</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>1.795078375666087</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>1.751927119831815</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>1.693325691658417</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>1.592484228281201</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>1.550169109357384</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>1.541600116844997</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>1.490126608659407</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>1.464315364575878</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>1.45152198421646</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>1.348314606741573</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>1.338782412626832</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>1.316655694535879</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>1.298989436317311</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>1.271296826968165</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>1.260876361173344</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>1.226042841037204</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>1.096447281784089</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>1.086941158178914</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>1.071025930101466</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>1.051156271899089</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>0.9951544834054082</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>0.9582863585118376</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>0.9332684435029057</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>0.9203859036386018</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>0.9019165727170236</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>0.8753191267649664</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>0.8737316798196166</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>0.8701088938675559</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>0.8032694475760992</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>0.7815349346115772</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>0.7711144688167562</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>0.7600698519939308</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>0.7490636704119851</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>0.7468996617812852</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>0.7328072153325818</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>0.7142652658097391</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>0.6834903094672354</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>0.6469897798517077</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>0.6304381805866722</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>0.599250936329588</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>0.599250936329588</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>0.599250936329588</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>0.5939665503047986</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>0.5731256187151565</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>0.5606166783461808</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>0.5606166783461808</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>0.5606166783461808</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>0.5217428645043085</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>0.4937458854509546</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>0.4905395935529082</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>0.4905395935529082</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>0.4791431792559188</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>0.4368658399098083</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>0.4279131007241606</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>0.4204625087596356</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>0.4050843090664453</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>0.3949967083607637</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>0.3949967083607637</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>0.3745318352059925</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>0.3745318352059925</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>0.3745318352059925</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>0.3535541496092297</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>0.350385423966363</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>0.350385423966363</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>0.3291639236339697</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>0.2969832751523993</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>0.2962475312705727</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>0.2633311389071758</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>0.2304147465437788</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>0.2304147465437788</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>0.2304147465437788</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>0.2304147465437788</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>0.2304147465437788</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>0.2247191011235955</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>0.2102312543798178</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>0.1653733621676632</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>0.149812734082397</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>0.149812734082397</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>0.149812734082397</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>0.1060085654920918</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>0.09874917709019092</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>1404</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Huara</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>0.09874917709019092</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>0.0894620823909994</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>0.0749063670411985</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>0.0749063670411985</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>0.0749063670411985</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Camiña</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>0.0749063670411985</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>1405</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Pica</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>0.07046223224351747</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>0.0700770847932726</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Colchane</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>0.0700770847932726</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>0.06548973601511447</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>0.03864761959291174</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>0.02120171309841835</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>0.01717671981907188</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>0.01563069869223154</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>0.01563069869223154</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>0.0150296298416879</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>0.01042046579482103</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>0.007872663250407946</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Alto Hospicio</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>0.005725573273023961</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>1101</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Iquique</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>0.003769193439718818</v>
       </c>
     </row>
   </sheetData>
